--- a/artfynd/A 14442-2025 artfynd.xlsx
+++ b/artfynd/A 14442-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>124610352</v>
       </c>
       <c r="B5" t="n">
-        <v>58158</v>
+        <v>58272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14442-2025 artfynd.xlsx
+++ b/artfynd/A 14442-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83325021</v>
+        <v>98184408</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 22786, Vg</t>
+          <t>Ekenäsudden, Gullringsbo, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334441.7345407974</v>
+        <v>334364</v>
       </c>
       <c r="R2" t="n">
-        <v>6404716.023105125</v>
+        <v>6404598</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +754,14 @@
           <t>Lerum</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>EFD39ADD-F72B-4F43-8D2D-DDD71AE3B838</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-10-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,31 +776,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Sjögren</t>
+          <t>Jon Håkansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Sjögren, Gunnar Flygh</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Bo Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85137361</v>
+        <v>94158961</v>
       </c>
       <c r="B3" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,16 +799,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>102992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,18 +819,13 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -857,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334364.1060570141</v>
+        <v>334364</v>
       </c>
       <c r="R3" t="n">
-        <v>6404598.476486853</v>
+        <v>6404598</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,27 +865,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På stenmur vid järnvägen</t>
+          <t>Kort sång</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +894,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -935,32 +912,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98184408</v>
+        <v>124610352</v>
       </c>
       <c r="B4" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,18 +942,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -991,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334364.1060570141</v>
+        <v>334364</v>
       </c>
       <c r="R4" t="n">
-        <v>6404598.476486853</v>
+        <v>6404598</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1021,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1019,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Håkansson</t>
+          <t>Bo Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1063,32 +1031,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124610352</v>
+        <v>85137361</v>
       </c>
       <c r="B5" t="n">
-        <v>58272</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103042</v>
+        <v>208260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1099,13 +1062,18 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1145,7 +1113,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1155,12 +1123,17 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stenmur vid järnvägen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,6 +1142,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1184,6 +1158,116 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>83325021</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>VGL Träd ID: 22786, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334442</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6404716</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>EFD39ADD-F72B-4F43-8D2D-DDD71AE3B838</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Sjögren, Gunnar Flygh</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14442-2025 artfynd.xlsx
+++ b/artfynd/A 14442-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98184408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94158961</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124610352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1158,6 +1178,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85137361</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,8 +1293,20 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83325021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>